--- a/セリフ編集/ナレーション・記事/黒田記者の目.xlsx
+++ b/セリフ編集/ナレーション・記事/黒田記者の目.xlsx
@@ -12480,7 +12480,7 @@
       </c>
       <c r="G454" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.matches}度の対戦は引き分け含み。両者がともに「次もやりたい」と表明している、業界では珍しい関係。記者として、こうした関係性が業界全体を底上げしていると見ている。</t>
+          <t xml:space="preserve">${d.matches}度の対戦を経てなお、両者がともに「次もやりたい」と表明している、業界では珍しい関係。記者として、こうした関係性が業界全体を底上げしていると見ている。</t>
         </is>
       </c>
     </row>
@@ -17421,7 +17421,7 @@
       </c>
       <c r="G637" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分け上等の塩試合フラグ立ってない？</t>
+          <t xml:space="preserve">決着放棄上等の塩試合フラグ立ってない？</t>
         </is>
       </c>
     </row>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="G749" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">譲らぬ両者。ドローだが、内容は十分</t>
+          <t xml:space="preserve">譲らぬ両者。決着はつかなかったが、内容は十分</t>
         </is>
       </c>
     </row>
@@ -20472,7 +20472,7 @@
       </c>
       <c r="G750" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">時間切れ引き分け。消化不良は否めない</t>
+          <t xml:space="preserve">時間切れで決着つかず。消化不良は否めない</t>
         </is>
       </c>
     </row>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="G752" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分け。ファンの消化不良感は否めないが、次への伏線にはなった</t>
+          <t xml:space="preserve">決着つかず。ファンの消化不良感は否めないが、次への伏線にはなった</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/ナレーション・記事/黒田記者の目.xlsx
+++ b/セリフ編集/ナレーション・記事/黒田記者の目.xlsx
@@ -9023,7 +9023,7 @@
       </c>
       <c r="H275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.name}。今季OVR +${d.ovrGain}の急成長だ。半年前まで脅威でもなんでもなかったのに、見違えた</t>
+          <t xml:space="preserve">${d.name}。今季総合力+${d.ovrGain}の急成長だ。半年前まで脅威でもなんでもなかったのに、見違えた</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="H277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.name}が化けている。OVR +${d.ovrGain}。放っておくと手がつけられなくなる</t>
+          <t xml:space="preserve">${d.name}が化けている。総合力+${d.ovrGain}。放っておくと手がつけられなくなる</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="H279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.name}、OVR +${d.ovrGain}。成長曲線が急すぎて、来季にはエース級になっていてもおかしくない</t>
+          <t xml:space="preserve">${d.name}、総合力+${d.ovrGain}。成長曲線が急すぎて、来季にはエース級になっていてもおかしくない</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="H280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本紙としては、${d.name}の成長は今季最大の発見の一つだと書いておく。OVR +${d.ovrGain}は偶然では出せない数字だ</t>
+          <t xml:space="preserve">本紙としては、${d.name}の成長は今季最大の発見の一つだと書いておく。総合力+${d.ovrGain}は偶然では出せない数字だ</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="H282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">数字は嘘をつかない。${d.name}のOVR +${d.ovrGain}という伸びは、この団体の育成方針が機能している証拠でもある</t>
+          <t xml:space="preserve">数字は嘘をつかない。${d.name}の総合力+${d.ovrGain}という伸びは、この団体の育成方針が機能している証拠でもある</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="H283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.orgName}の看板、${d.name}。OVR ${d.ovr}に人気${d.pop}——実力と集客力を兼ね備えた正真正銘のエースだ</t>
+          <t xml:space="preserve">${d.orgName}の看板、${d.name}。総合力${d.ovr}に人気${d.pop}——実力と集客力を兼ね備えた正真正銘のエースだ</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="H285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.name}は人気${d.pop}。OVRはまだ発展途上だが、ファンを呼べるのは才能の証だ</t>
+          <t xml:space="preserve">${d.name}は人気${d.pop}。総合力はまだ発展途上だが、ファンを呼べるのは才能の証だ</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="H286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.name}——OVR ${d.ovr}、人気${d.pop}。こちらのエースと真正面からぶつかれる数少ない相手だ</t>
+          <t xml:space="preserve">${d.name}——総合力${d.ovr}、人気${d.pop}。こちらのエースと真正面からぶつかれる数少ない相手だ</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="H287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.name}、OVR ${d.ovr}で人気${d.pop}。実力と人気のバランスが良く、どのカードにも組み込める</t>
+          <t xml:space="preserve">${d.name}、総合力${d.ovr}で人気${d.pop}。実力と人気のバランスが良く、どのカードにも組み込める</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="H289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対策なしで${d.name}に当たれば、興行ごと持っていかれる。OVR ${d.ovr}に人気${d.pop}は反則だ</t>
+          <t xml:space="preserve">対策なしで${d.name}に当たれば、興行ごと持っていかれる。総合力${d.ovr}に人気${d.pop}は反則だ</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="H293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.orgName}の集客の要は${d.name}。OVR ${d.ovr}と伸びしろもある。要注意だ</t>
+          <t xml:space="preserve">${d.orgName}の集客の要は${d.name}。総合力${d.ovr}と伸びしろもある。要注意だ</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="H294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.orgName}の人気看板は${d.name}。OVRは発展途上だが、カリスマ性は数字に出ている</t>
+          <t xml:space="preserve">${d.orgName}の人気看板は${d.name}。総合力は発展途上だが、カリスマ性は数字に出ている</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="H295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本紙としては、${d.name}は${d.orgName}そのものを背負う存在だと書いておく。OVR ${d.ovr}、人気${d.pop}——この組み合わせは反則だ</t>
+          <t xml:space="preserve">本紙としては、${d.name}は${d.orgName}そのものを背負う存在だと書いておく。総合力${d.ovr}、人気${d.pop}——この組み合わせは反則だ</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="H296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本紙は${d.name}を要警戒人物リストに入れておく。OVR ${d.ovr}に人気${d.pop}は十分に脅威だ</t>
+          <t xml:space="preserve">本紙は${d.name}を要警戒人物リストに入れておく。総合力${d.ovr}に人気${d.pop}は十分に脅威だ</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="H298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">40年見てきた中で、OVR ${d.ovr}と人気${d.pop}を両立する選手は一握りだ。${d.name}はその一握りに入っている</t>
+          <t xml:space="preserve">40年見てきた中で、総合力${d.ovr}と人気${d.pop}を両立する選手は一握りだ。${d.name}はその一握りに入っている</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="H301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">数字は嘘をつかない。${d.name}のOVR ${d.ovr}・人気${d.pop}はトップクラスの証だ</t>
+          <t xml:space="preserve">数字は嘘をつかない。${d.name}の総合力${d.ovr}・人気${d.pop}はトップクラスの証だ</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="H312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.name}（${d.age}歳）。OVR ${d.ovr} は通過点でしかない、というのが本紙の見立てだ</t>
+          <t xml:space="preserve">${d.name}（${d.age}歳）。総合力${d.ovr} は通過点でしかない、というのが本紙の見立てだ</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="H313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.age}歳という年齢、OVR ${d.ovr} という数字。この組み合わせが意味するのは「これからが本番」ということだ</t>
+          <t xml:space="preserve">${d.age}歳という年齢、総合力${d.ovr} という数字。この組み合わせが意味するのは「これからが本番」ということだ</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.name}（${d.age}歳）はキャリアの中核に差し掛かっている。OVR ${d.ovr} で${d.orgName}の屋台骨を支える存在</t>
+          <t xml:space="preserve">${d.name}（${d.age}歳）はキャリアの中核に差し掛かっている。総合力${d.ovr} で${d.orgName}の屋台骨を支える存在</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="H324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.age}歳の${d.name}は、もはや団体の信用そのものだ。OVR ${d.ovr} に裏付けされた安定感がある</t>
+          <t xml:space="preserve">${d.age}歳の${d.name}は、もはや団体の信用そのものだ。総合力${d.ovr} に裏付けされた安定感がある</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="H325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">${d.age}歳の${d.name}。OVR ${d.ovr} を維持し続けるベテランの存在は、若手の壁として機能している</t>
+          <t xml:space="preserve">${d.age}歳の${d.name}。総合力${d.ovr} を維持し続けるベテランの存在は、若手の壁として機能している</t>
         </is>
       </c>
     </row>
